--- a/public/templates/invoice/seikyu_advance_shiho.xlsx
+++ b/public/templates/invoice/seikyu_advance_shiho.xlsx
@@ -8,10 +8,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書（前受金）司" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="一般社団法人いきいき">抽出元!$A$3</definedName>
     <definedName name="株式会社オーシャン">抽出元!$A$4</definedName>
@@ -4385,166 +4381,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="入力元"/>
-      <sheetName val="簡易契約書 "/>
-      <sheetName val="簡易契約書 (行・司)"/>
-      <sheetName val="契約書★財産調査あり（連名）"/>
-      <sheetName val="契約書★財産調査なし（連名）"/>
-      <sheetName val="契約書★財産調査あり（行単独）"/>
-      <sheetName val="契約書(遺言など単独)★財産調査なし "/>
-      <sheetName val="委任状  (法定相続情報証明）"/>
-      <sheetName val="委任状（行・司連名）"/>
-      <sheetName val="委任状（行・司連連名）預金解約あり"/>
-      <sheetName val="委任状（行・司連名）登記のみ"/>
-      <sheetName val="委任状（行のみ）相続"/>
-      <sheetName val="委任状 (司のみ)相続登記 "/>
-      <sheetName val="委任状 (行)遺言"/>
-      <sheetName val="委任状 (行司)贈与・信託"/>
-      <sheetName val="委任状 (司)贈与・信託 "/>
-      <sheetName val="委任状 (遺言検索のみ)"/>
-      <sheetName val="原本預かり証"/>
-      <sheetName val="原本受領証"/>
-      <sheetName val="郵送書類確認票"/>
-      <sheetName val="契約書（1％）"/>
-      <sheetName val="契約書（執行）"/>
-      <sheetName val="請求書（前受金）行"/>
-      <sheetName val="請求書（前受金）司"/>
-      <sheetName val="立替実費 行 "/>
-      <sheetName val="立替実費 司"/>
-      <sheetName val="請求書 (確定)行"/>
-      <sheetName val="請求書 (確定) 司"/>
-      <sheetName val="領収書（前受金）行"/>
-      <sheetName val="領収書（前受金）司"/>
-      <sheetName val="領収書 (確定)行"/>
-      <sheetName val="領収書 (確定)司"/>
-      <sheetName val="角２封筒"/>
-      <sheetName val="長形３号（白）"/>
-      <sheetName val="長形３号 (茶)"/>
-      <sheetName val="抽出元"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="入力元"/>
-      <sheetName val="簡易契約書 "/>
-      <sheetName val="簡易契約書 (行・司)"/>
-      <sheetName val="契約書★財産調査あり（連名）"/>
-      <sheetName val="契約書★財産調査なし（連名）"/>
-      <sheetName val="契約書★財産調査あり（行単独）"/>
-      <sheetName val="契約書(遺言など単独)★財産調査なし "/>
-      <sheetName val="委任状  (法定相続情報証明）"/>
-      <sheetName val="委任状"/>
-      <sheetName val="委任状（預金解約あり） "/>
-      <sheetName val="委任状 (登記のみ) "/>
-      <sheetName val="委任状 (遺言一般)"/>
-      <sheetName val="委任状 (贈与・信託)"/>
-      <sheetName val="委任状 (遺言検索のみ)"/>
-      <sheetName val="原本預かり証"/>
-      <sheetName val="原本受領証"/>
-      <sheetName val="郵送書類確認票"/>
-      <sheetName val="返送書類ご案内一覧 "/>
-      <sheetName val="契約書（1％）"/>
-      <sheetName val="契約書（執行）"/>
-      <sheetName val="請求書（前受金）行"/>
-      <sheetName val="請求書（前受金）司"/>
-      <sheetName val="立替実費"/>
-      <sheetName val="請求書 (確定)行"/>
-      <sheetName val="請求書 (確定) 司"/>
-      <sheetName val="領収書（前受金）行"/>
-      <sheetName val="領収書（前受金）司"/>
-      <sheetName val="領収書 (確定)行"/>
-      <sheetName val="領収書 (確定) 司"/>
-      <sheetName val="角２封筒"/>
-      <sheetName val="長形３号（白）"/>
-      <sheetName val="長形３号 (茶)"/>
-      <sheetName val="抽出元"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>

--- a/public/templates/invoice/seikyu_advance_shiho.xlsx
+++ b/public/templates/invoice/seikyu_advance_shiho.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="10" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="10" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="請求書（前受金）司" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <definedName name="徽章4">INDIRECT(#REF!)</definedName>
     <definedName name="行政書士法人">抽出元!$A$1</definedName>
     <definedName name="司法書士法人">抽出元!$A$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'請求書（前受金）司'!$A$1:$Y$41</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -748,7 +749,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="126">
+  <borders count="127">
     <border>
       <left/>
       <right/>
@@ -2199,11 +2200,17 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45"/>
   </cellStyleXfs>
-  <cellXfs count="677">
+  <cellXfs count="679">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -3751,6 +3758,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4582,7 +4593,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AJ1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
@@ -4735,7 +4746,7 @@
       <c r="AJ3" s="612" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1" s="359">
-      <c r="A4" s="621" t="inlineStr">
+      <c r="A4" s="677" t="inlineStr">
         <is>
           <t>御　請　求　書</t>
         </is>
@@ -4753,31 +4764,31 @@
       <c r="AJ4" s="612" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1" s="359">
-      <c r="A5" s="623" t="n"/>
-      <c r="B5" s="623" t="n"/>
-      <c r="C5" s="623" t="n"/>
-      <c r="D5" s="623" t="n"/>
-      <c r="E5" s="623" t="n"/>
-      <c r="F5" s="623" t="n"/>
-      <c r="G5" s="623" t="n"/>
-      <c r="H5" s="623" t="n"/>
-      <c r="I5" s="623" t="n"/>
-      <c r="J5" s="623" t="n"/>
-      <c r="K5" s="623" t="n"/>
-      <c r="L5" s="623" t="n"/>
-      <c r="M5" s="623" t="n"/>
-      <c r="N5" s="623" t="n"/>
-      <c r="O5" s="623" t="n"/>
-      <c r="P5" s="623" t="n"/>
-      <c r="Q5" s="623" t="n"/>
-      <c r="R5" s="623" t="n"/>
-      <c r="S5" s="623" t="n"/>
-      <c r="T5" s="623" t="n"/>
-      <c r="U5" s="623" t="n"/>
-      <c r="V5" s="623" t="n"/>
-      <c r="W5" s="623" t="n"/>
-      <c r="X5" s="623" t="n"/>
-      <c r="Y5" s="623" t="n"/>
+      <c r="A5" s="678" t="n"/>
+      <c r="B5" s="678" t="n"/>
+      <c r="C5" s="678" t="n"/>
+      <c r="D5" s="678" t="n"/>
+      <c r="E5" s="678" t="n"/>
+      <c r="F5" s="678" t="n"/>
+      <c r="G5" s="678" t="n"/>
+      <c r="H5" s="678" t="n"/>
+      <c r="I5" s="678" t="n"/>
+      <c r="J5" s="678" t="n"/>
+      <c r="K5" s="678" t="n"/>
+      <c r="L5" s="678" t="n"/>
+      <c r="M5" s="678" t="n"/>
+      <c r="N5" s="678" t="n"/>
+      <c r="O5" s="678" t="n"/>
+      <c r="P5" s="678" t="n"/>
+      <c r="Q5" s="678" t="n"/>
+      <c r="R5" s="678" t="n"/>
+      <c r="S5" s="678" t="n"/>
+      <c r="T5" s="678" t="n"/>
+      <c r="U5" s="678" t="n"/>
+      <c r="V5" s="678" t="n"/>
+      <c r="W5" s="678" t="n"/>
+      <c r="X5" s="678" t="n"/>
+      <c r="Y5" s="678" t="n"/>
       <c r="Z5" s="614" t="n"/>
       <c r="AA5" s="620" t="n"/>
       <c r="AB5" s="620" t="n"/>
@@ -4809,7 +4820,7 @@
       <c r="P6" s="248" t="n"/>
       <c r="Q6" s="624" t="inlineStr">
         <is>
-          <t xml:space="preserve">　登録番号：T8-0200-0501-1099</t>
+          <t>登録番号：T8-0200-0501-1099</t>
         </is>
       </c>
       <c r="Z6" s="614" t="n"/>
@@ -5237,7 +5248,7 @@
     </row>
     <row r="17" ht="28.5" customHeight="1" s="359">
       <c r="A17" s="7" t="n"/>
-      <c r="B17" s="644" t="inlineStr">
+      <c r="B17" s="646" t="inlineStr">
         <is>
           <t>件　　　　名</t>
         </is>
@@ -42731,78 +42742,78 @@
   </sheetData>
   <mergeCells count="73">
     <mergeCell ref="V26:Y26"/>
+    <mergeCell ref="B28:T28"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="Q14:Y14"/>
+    <mergeCell ref="D14:I15"/>
+    <mergeCell ref="D10:K10"/>
     <mergeCell ref="B30:T30"/>
     <mergeCell ref="V25:Y25"/>
     <mergeCell ref="R10:V10"/>
     <mergeCell ref="B24:Q24"/>
+    <mergeCell ref="R21:T21"/>
     <mergeCell ref="R20:T20"/>
+    <mergeCell ref="V22:Y22"/>
+    <mergeCell ref="B20:Q20"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="Q15:Y15"/>
     <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="U17:Y17"/>
+    <mergeCell ref="Q6:Y6"/>
+    <mergeCell ref="Q13:W13"/>
+    <mergeCell ref="V21:Y21"/>
     <mergeCell ref="B26:Q26"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="R22:T22"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="I40:X40"/>
     <mergeCell ref="G37:N37"/>
     <mergeCell ref="B25:Q25"/>
+    <mergeCell ref="J14:K15"/>
     <mergeCell ref="N14:O14"/>
-    <mergeCell ref="J14:K15"/>
+    <mergeCell ref="J8:K9"/>
+    <mergeCell ref="V23:Y23"/>
     <mergeCell ref="Q11:Y11"/>
+    <mergeCell ref="B22:Q22"/>
+    <mergeCell ref="B31:T31"/>
+    <mergeCell ref="V2:W3"/>
+    <mergeCell ref="F3:I3"/>
     <mergeCell ref="B18:Q18"/>
     <mergeCell ref="B27:Q27"/>
+    <mergeCell ref="X2:Y3"/>
     <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="S26:U26"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="V29:Y29"/>
+    <mergeCell ref="B37:E40"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="B21:Q21"/>
     <mergeCell ref="S25:U25"/>
+    <mergeCell ref="N13:O13"/>
     <mergeCell ref="A4:Y5"/>
+    <mergeCell ref="V28:Y28"/>
     <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="V24:Y24"/>
+    <mergeCell ref="R24:U24"/>
+    <mergeCell ref="W10:Y10"/>
     <mergeCell ref="Q12:Y12"/>
     <mergeCell ref="V31:Y31"/>
     <mergeCell ref="N15:O15"/>
+    <mergeCell ref="B23:T23"/>
     <mergeCell ref="S27:U27"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="B28:T28"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="Q15:Y15"/>
-    <mergeCell ref="U17:Y17"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="B31:T31"/>
-    <mergeCell ref="S26:U26"/>
-    <mergeCell ref="V19:Y19"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="V28:Y28"/>
-    <mergeCell ref="W10:Y10"/>
-    <mergeCell ref="B23:T23"/>
     <mergeCell ref="B17:Q17"/>
     <mergeCell ref="B8:I9"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="R19:T19"/>
     <mergeCell ref="V30:Y30"/>
     <mergeCell ref="M38:Q38"/>
-    <mergeCell ref="B19:Q19"/>
-    <mergeCell ref="Q14:Y14"/>
-    <mergeCell ref="D14:I15"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="B20:Q20"/>
-    <mergeCell ref="Q6:Y6"/>
-    <mergeCell ref="Q13:W13"/>
-    <mergeCell ref="V21:Y21"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="J8:K9"/>
-    <mergeCell ref="V23:Y23"/>
-    <mergeCell ref="V2:W3"/>
-    <mergeCell ref="X2:Y3"/>
-    <mergeCell ref="V24:Y24"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="R19:T19"/>
     <mergeCell ref="B14:C15"/>
     <mergeCell ref="B29:T29"/>
     <mergeCell ref="V27:Y27"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="V22:Y22"/>
-    <mergeCell ref="I40:X40"/>
-    <mergeCell ref="B22:Q22"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B37:E40"/>
-    <mergeCell ref="B21:Q21"/>
-    <mergeCell ref="R24:U24"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="B19:Q19"/>
   </mergeCells>
   <conditionalFormatting sqref="B8:I9 F3:I3">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -42827,6 +42838,6 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.5905511811023623" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="93"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>